--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3613,6 +3613,112 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121521527</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78343</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>584670</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7048475</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3719,6 +3719,326 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121540452</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78344</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>584427</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7048336</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Grövre tallstubbe med brandljud</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121540453</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98016</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>584504</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7048314</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121540451</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78344</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>584430</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7048337</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>På grövre tallstubbe med brandljud</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3618,7 +3618,7 @@
         <v>121521527</v>
       </c>
       <c r="B28" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121540453</v>
+        <v>121540451</v>
       </c>
       <c r="B30" t="n">
-        <v>98016</v>
+        <v>78344</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3840,42 +3840,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584504</v>
+        <v>584430</v>
       </c>
       <c r="R30" t="n">
-        <v>7048314</v>
+        <v>7048337</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3918,6 +3914,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>På grövre tallstubbe med brandljud</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3934,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121540451</v>
+        <v>121540453</v>
       </c>
       <c r="B31" t="n">
-        <v>78344</v>
+        <v>98021</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3946,38 +3947,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584430</v>
+        <v>584504</v>
       </c>
       <c r="R31" t="n">
-        <v>7048337</v>
+        <v>7048314</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4020,11 +4025,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>På grövre tallstubbe med brandljud</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3618,7 +3618,7 @@
         <v>121521527</v>
       </c>
       <c r="B28" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121540452</v>
+        <v>121540453</v>
       </c>
       <c r="B29" t="n">
-        <v>78344</v>
+        <v>98022</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,38 +3733,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584427</v>
+        <v>584504</v>
       </c>
       <c r="R29" t="n">
-        <v>7048336</v>
+        <v>7048314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3807,11 +3811,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Grövre tallstubbe med brandljud</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3831,7 +3830,7 @@
         <v>121540451</v>
       </c>
       <c r="B30" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121540453</v>
+        <v>121540452</v>
       </c>
       <c r="B31" t="n">
-        <v>98021</v>
+        <v>78345</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3947,42 +3946,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584504</v>
+        <v>584427</v>
       </c>
       <c r="R31" t="n">
-        <v>7048314</v>
+        <v>7048336</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,6 +4020,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Grövre tallstubbe med brandljud</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121540453</v>
+        <v>121540451</v>
       </c>
       <c r="B29" t="n">
-        <v>98022</v>
+        <v>78345</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,42 +3733,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584504</v>
+        <v>584430</v>
       </c>
       <c r="R29" t="n">
-        <v>7048314</v>
+        <v>7048337</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3811,6 +3807,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>På grövre tallstubbe med brandljud</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3827,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121540451</v>
+        <v>121540453</v>
       </c>
       <c r="B30" t="n">
-        <v>78345</v>
+        <v>98022</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,38 +3840,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584430</v>
+        <v>584504</v>
       </c>
       <c r="R30" t="n">
-        <v>7048337</v>
+        <v>7048314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3913,11 +3918,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>På grövre tallstubbe med brandljud</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121540451</v>
+        <v>121540453</v>
       </c>
       <c r="B29" t="n">
-        <v>78345</v>
+        <v>98022</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,38 +3733,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584430</v>
+        <v>584504</v>
       </c>
       <c r="R29" t="n">
-        <v>7048337</v>
+        <v>7048314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3807,11 +3811,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>På grövre tallstubbe med brandljud</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3828,10 +3827,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121540453</v>
+        <v>121540452</v>
       </c>
       <c r="B30" t="n">
-        <v>98022</v>
+        <v>78345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3840,42 +3839,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584504</v>
+        <v>584427</v>
       </c>
       <c r="R30" t="n">
-        <v>7048314</v>
+        <v>7048336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3918,6 +3913,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Grövre tallstubbe med brandljud</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3934,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121540452</v>
+        <v>121540451</v>
       </c>
       <c r="B31" t="n">
         <v>78345</v>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584427</v>
+        <v>584430</v>
       </c>
       <c r="R31" t="n">
-        <v>7048336</v>
+        <v>7048337</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grövre tallstubbe med brandljud</t>
+          <t>På grövre tallstubbe med brandljud</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3618,7 +3618,7 @@
         <v>121521527</v>
       </c>
       <c r="B28" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>121540453</v>
       </c>
       <c r="B29" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>121540452</v>
       </c>
       <c r="B30" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>121540451</v>
       </c>
       <c r="B31" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3827,7 +3827,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121540451</v>
+        <v>121540452</v>
       </c>
       <c r="B30" t="n">
         <v>78352</v>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584430</v>
+        <v>584427</v>
       </c>
       <c r="R30" t="n">
-        <v>7048337</v>
+        <v>7048336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>På grövre tallstubbe med brandljud</t>
+          <t>Grövre tallstubbe med brandljud</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121540452</v>
+        <v>121540451</v>
       </c>
       <c r="B31" t="n">
         <v>78352</v>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584427</v>
+        <v>584430</v>
       </c>
       <c r="R31" t="n">
-        <v>7048336</v>
+        <v>7048337</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grövre tallstubbe med brandljud</t>
+          <t>På grövre tallstubbe med brandljud</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121540453</v>
+        <v>121540452</v>
       </c>
       <c r="B29" t="n">
-        <v>98030</v>
+        <v>78352</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,42 +3733,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584504</v>
+        <v>584427</v>
       </c>
       <c r="R29" t="n">
-        <v>7048314</v>
+        <v>7048336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3811,6 +3807,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Grövre tallstubbe med brandljud</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3827,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121540452</v>
+        <v>121540453</v>
       </c>
       <c r="B30" t="n">
-        <v>78352</v>
+        <v>98030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,38 +3840,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ramsele, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584427</v>
+        <v>584504</v>
       </c>
       <c r="R30" t="n">
-        <v>7048336</v>
+        <v>7048314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3913,11 +3918,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Grövre tallstubbe med brandljud</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3721,7 +3721,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121540452</v>
+        <v>121540451</v>
       </c>
       <c r="B29" t="n">
         <v>78352</v>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584427</v>
+        <v>584430</v>
       </c>
       <c r="R29" t="n">
-        <v>7048336</v>
+        <v>7048337</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grövre tallstubbe med brandljud</t>
+          <t>På grövre tallstubbe med brandljud</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121540451</v>
+        <v>121540452</v>
       </c>
       <c r="B31" t="n">
         <v>78352</v>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584430</v>
+        <v>584427</v>
       </c>
       <c r="R31" t="n">
-        <v>7048337</v>
+        <v>7048336</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>På grövre tallstubbe med brandljud</t>
+          <t>Grövre tallstubbe med brandljud</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 41031-2020 artfynd.xlsx
+++ b/artfynd/A 41031-2020 artfynd.xlsx
@@ -3721,7 +3721,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121540451</v>
+        <v>121540452</v>
       </c>
       <c r="B29" t="n">
         <v>78352</v>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584430</v>
+        <v>584427</v>
       </c>
       <c r="R29" t="n">
-        <v>7048337</v>
+        <v>7048336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>På grövre tallstubbe med brandljud</t>
+          <t>Grövre tallstubbe med brandljud</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121540452</v>
+        <v>121540451</v>
       </c>
       <c r="B31" t="n">
         <v>78352</v>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584427</v>
+        <v>584430</v>
       </c>
       <c r="R31" t="n">
-        <v>7048336</v>
+        <v>7048337</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grövre tallstubbe med brandljud</t>
+          <t>På grövre tallstubbe med brandljud</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
